--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.58665032331182</v>
+        <v>7.407830677538171</v>
       </c>
       <c r="D2" t="n">
-        <v>36.42210986468836</v>
+        <v>5.918592853011859</v>
       </c>
       <c r="E2" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F2" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.53533622258381</v>
+        <v>9.024492136169869</v>
       </c>
       <c r="D3" t="n">
-        <v>27.8046203638936</v>
+        <v>4.518250809132711</v>
       </c>
       <c r="E3" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F3" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.52775219053555</v>
+        <v>10.81075973096203</v>
       </c>
       <c r="D4" t="n">
-        <v>30.21447567272917</v>
+        <v>4.90985229681849</v>
       </c>
       <c r="E4" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F4" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.09115423025732</v>
+        <v>2.777312562416814</v>
       </c>
       <c r="D5" t="n">
-        <v>6.076013533926328</v>
+        <v>0.9873521992630283</v>
       </c>
       <c r="E5" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F5" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.87521471880791</v>
+        <v>4.204722391806285</v>
       </c>
       <c r="D6" t="n">
-        <v>18.72852838493648</v>
+        <v>3.043385862552178</v>
       </c>
       <c r="E6" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F6" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.835580632832212</v>
+        <v>0.7857818528352344</v>
       </c>
       <c r="D7" t="n">
-        <v>8.224767976904198</v>
+        <v>1.336524796246932</v>
       </c>
       <c r="E7" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F7" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.59654890794663</v>
+        <v>7.734439197541328</v>
       </c>
       <c r="D8" t="n">
-        <v>39.92154806617599</v>
+        <v>6.4872515607536</v>
       </c>
       <c r="E8" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F8" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.87749497575795</v>
+        <v>5.830092933560667</v>
       </c>
       <c r="D9" t="n">
-        <v>27.65874091767012</v>
+        <v>4.494545399121394</v>
       </c>
       <c r="E9" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F9" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.65991756712802</v>
+        <v>7.419736604658303</v>
       </c>
       <c r="D10" t="n">
-        <v>37.43501035127412</v>
+        <v>6.083189182082044</v>
       </c>
       <c r="E10" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F10" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>60.71394971207027</v>
+        <v>9.86601682821142</v>
       </c>
       <c r="D11" t="n">
-        <v>18.18066063562101</v>
+        <v>2.954357353288415</v>
       </c>
       <c r="E11" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F11" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.76879417932658</v>
+        <v>3.699929054140569</v>
       </c>
       <c r="D12" t="n">
-        <v>6.466620163912772</v>
+        <v>1.050825776635826</v>
       </c>
       <c r="E12" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F12" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.45840136673291</v>
+        <v>7.061990222094098</v>
       </c>
       <c r="D13" t="n">
-        <v>43.33814825314536</v>
+        <v>7.042449091136121</v>
       </c>
       <c r="E13" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F13" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.90304975141036</v>
+        <v>3.884245584604184</v>
       </c>
       <c r="D14" t="n">
-        <v>23.65136590093575</v>
+        <v>3.843346958902059</v>
       </c>
       <c r="E14" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F14" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>76.12234115333766</v>
+        <v>12.36988043741737</v>
       </c>
       <c r="D15" t="n">
-        <v>15.5941829337974</v>
+        <v>2.534054726742078</v>
       </c>
       <c r="E15" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F15" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>12.06732867564898</v>
+        <v>1.96094090979296</v>
       </c>
       <c r="D16" t="n">
-        <v>11.59297217716993</v>
+        <v>1.883857978790113</v>
       </c>
       <c r="E16" t="n">
-        <v>20.17936496245217</v>
+        <v>3.279146806398478</v>
       </c>
       <c r="F16" t="n">
-        <v>12.07650046354641</v>
+        <v>1.962431325326292</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
